--- a/AAII_Financials/Yearly/NPWR_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/NPWR_YR_FIN.xlsx
@@ -914,7 +914,7 @@
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>1439800</v>
+        <v>1439400</v>
       </c>
       <c r="E14" s="3">
         <v>25700</v>
@@ -999,7 +999,7 @@
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>279500</v>
+        <v>280000</v>
       </c>
       <c r="E17" s="3">
         <v>181600</v>
@@ -1035,7 +1035,7 @@
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>-279500</v>
+        <v>-280000</v>
       </c>
       <c r="E18" s="3">
         <v>-181300</v>
@@ -1123,7 +1123,7 @@
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>-195800</v>
+        <v>-196300</v>
       </c>
       <c r="E21" s="3">
         <v>-99300</v>
